--- a/tests/test_data/mock_master.xlsx
+++ b/tests/test_data/mock_master.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-80520" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="BrewSync" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,11 +47,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,14 +438,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" s="1" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>B9999</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C2" t="n">
-        <v>60</v>
+      <c r="B3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
